--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_021.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_021.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="162">
   <si>
     <t>Sezione</t>
   </si>
@@ -297,6 +297,12 @@
   </si>
   <si>
     <t>evento.intestatari[0]</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto nascita intestatario</t>
@@ -550,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.390625" customWidth="true" bestFit="true"/>
@@ -2864,39 +2870,39 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>100</v>
@@ -2910,7 +2916,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>101</v>
@@ -2919,7 +2925,7 @@
         <v>12</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>102</v>
@@ -2933,7 +2939,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>103</v>
@@ -2942,7 +2948,7 @@
         <v>12</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>104</v>
@@ -2956,7 +2962,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>105</v>
@@ -2965,7 +2971,7 @@
         <v>12</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>106</v>
@@ -2979,7 +2985,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>107</v>
@@ -2988,10 +2994,10 @@
         <v>12</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3002,19 +3008,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3025,7 +3031,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>110</v>
@@ -3034,10 +3040,10 @@
         <v>12</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3048,19 +3054,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -3071,7 +3077,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>113</v>
@@ -3080,7 +3086,7 @@
         <v>12</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>114</v>
@@ -3094,7 +3100,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>115</v>
@@ -3103,7 +3109,7 @@
         <v>12</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>116</v>
@@ -3117,7 +3123,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>117</v>
@@ -3126,7 +3132,7 @@
         <v>12</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>118</v>
@@ -3140,39 +3146,39 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B114" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>124</v>
@@ -3186,7 +3192,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>125</v>
@@ -3195,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>126</v>
@@ -3209,19 +3215,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3232,16 +3238,16 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>129</v>
@@ -3255,16 +3261,16 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>131</v>
@@ -3278,7 +3284,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>132</v>
@@ -3287,7 +3293,7 @@
         <v>12</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>133</v>
@@ -3301,42 +3307,42 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="C120" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3347,19 +3353,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="C122" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3370,19 +3376,19 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
@@ -3393,7 +3399,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>138</v>
@@ -3402,7 +3408,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>139</v>
@@ -3416,7 +3422,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>140</v>
@@ -3425,7 +3431,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>141</v>
@@ -3439,7 +3445,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>142</v>
@@ -3448,7 +3454,7 @@
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>143</v>
@@ -3462,39 +3468,39 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="C127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E127" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>124</v>
@@ -3508,7 +3514,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>125</v>
@@ -3517,7 +3523,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>126</v>
@@ -3531,19 +3537,19 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
@@ -3554,7 +3560,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>138</v>
@@ -3563,7 +3569,7 @@
         <v>12</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>139</v>
@@ -3577,7 +3583,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>140</v>
@@ -3586,7 +3592,7 @@
         <v>12</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>141</v>
@@ -3600,7 +3606,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>142</v>
@@ -3609,7 +3615,7 @@
         <v>12</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>143</v>
@@ -3623,19 +3629,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="C134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D134" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
@@ -3646,7 +3652,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>148</v>
@@ -3655,7 +3661,7 @@
         <v>12</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>149</v>
@@ -3669,19 +3675,19 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
@@ -3692,16 +3698,16 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>155</v>
@@ -3715,7 +3721,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>156</v>
@@ -3724,7 +3730,7 @@
         <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>157</v>
@@ -3738,7 +3744,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>158</v>
@@ -3747,7 +3753,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>159</v>
@@ -3756,6 +3762,29 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140" s="2" t="s">
         <v>21</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_021.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_021.xlsx
@@ -41,25 +41,25 @@
     <t>Decreto del Tribunale</t>
   </si>
   <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Sentenza straniera</t>
+  </si>
+  <si>
+    <t>Nota di trasmissione da parte dell’autorità consolare o diplomatica</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>193.3</t>
+  </si>
+  <si>
     <t>SI</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Sentenza straniera</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Nota di trasmissione da parte dell’autorità consolare o diplomatica</t>
-  </si>
-  <si>
-    <t>Formula</t>
-  </si>
-  <si>
-    <t>193.3</t>
   </si>
   <si>
     <t>Si puo' ignorare la sezione per</t>
@@ -634,7 +634,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -654,10 +654,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
@@ -674,13 +674,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -726,7 +726,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
@@ -749,7 +749,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
@@ -772,7 +772,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>19</v>
@@ -795,7 +795,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>19</v>
@@ -818,7 +818,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>30</v>
@@ -841,7 +841,7 @@
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>30</v>
@@ -864,7 +864,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>30</v>
@@ -887,7 +887,7 @@
         <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>30</v>
@@ -910,7 +910,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>30</v>
@@ -933,7 +933,7 @@
         <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>30</v>
@@ -956,7 +956,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>30</v>
@@ -979,7 +979,7 @@
         <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>30</v>
@@ -1002,7 +1002,7 @@
         <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>30</v>
@@ -1025,7 +1025,7 @@
         <v>49</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>30</v>
@@ -1048,7 +1048,7 @@
         <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>30</v>
@@ -1071,7 +1071,7 @@
         <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>30</v>
@@ -1094,7 +1094,7 @@
         <v>55</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>30</v>
@@ -1117,7 +1117,7 @@
         <v>57</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>30</v>
@@ -1140,7 +1140,7 @@
         <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
@@ -1163,7 +1163,7 @@
         <v>61</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
@@ -1186,7 +1186,7 @@
         <v>63</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
@@ -1209,7 +1209,7 @@
         <v>65</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
@@ -1232,7 +1232,7 @@
         <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
@@ -1255,7 +1255,7 @@
         <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -1278,7 +1278,7 @@
         <v>71</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -1301,7 +1301,7 @@
         <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
@@ -1324,7 +1324,7 @@
         <v>75</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
@@ -1347,7 +1347,7 @@
         <v>77</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
@@ -1370,7 +1370,7 @@
         <v>79</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
@@ -1393,7 +1393,7 @@
         <v>81</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>30</v>
@@ -1416,7 +1416,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>30</v>
@@ -1439,7 +1439,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>30</v>
@@ -1462,7 +1462,7 @@
         <v>87</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>30</v>
@@ -1485,7 +1485,7 @@
         <v>89</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>30</v>
@@ -1508,7 +1508,7 @@
         <v>91</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>30</v>
@@ -1531,7 +1531,7 @@
         <v>93</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
@@ -1554,7 +1554,7 @@
         <v>29</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>96</v>
@@ -1577,7 +1577,7 @@
         <v>33</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>96</v>
@@ -1600,7 +1600,7 @@
         <v>35</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>96</v>
@@ -1623,7 +1623,7 @@
         <v>37</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>96</v>
@@ -1646,7 +1646,7 @@
         <v>39</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>96</v>
@@ -1669,7 +1669,7 @@
         <v>41</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>96</v>
@@ -1692,7 +1692,7 @@
         <v>43</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>96</v>
@@ -1715,7 +1715,7 @@
         <v>45</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>96</v>
@@ -1738,7 +1738,7 @@
         <v>47</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>96</v>
@@ -1761,7 +1761,7 @@
         <v>49</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>96</v>
@@ -1784,7 +1784,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>96</v>
@@ -1807,7 +1807,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>96</v>
@@ -1830,7 +1830,7 @@
         <v>55</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>96</v>
@@ -1853,7 +1853,7 @@
         <v>57</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>96</v>
@@ -1876,7 +1876,7 @@
         <v>59</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>96</v>
@@ -1899,7 +1899,7 @@
         <v>61</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>96</v>
@@ -1922,7 +1922,7 @@
         <v>63</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>96</v>
@@ -1945,7 +1945,7 @@
         <v>65</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>96</v>
@@ -1968,7 +1968,7 @@
         <v>67</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>96</v>
@@ -1991,7 +1991,7 @@
         <v>69</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>96</v>
@@ -2014,7 +2014,7 @@
         <v>71</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>96</v>
@@ -2037,7 +2037,7 @@
         <v>73</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>96</v>
@@ -2060,7 +2060,7 @@
         <v>75</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>96</v>
@@ -2083,7 +2083,7 @@
         <v>77</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>96</v>
@@ -2106,7 +2106,7 @@
         <v>79</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>96</v>
@@ -2129,7 +2129,7 @@
         <v>81</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>96</v>
@@ -2152,7 +2152,7 @@
         <v>83</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>96</v>
@@ -2175,7 +2175,7 @@
         <v>85</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>96</v>
@@ -2198,7 +2198,7 @@
         <v>87</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>96</v>
@@ -2221,7 +2221,7 @@
         <v>89</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>96</v>
@@ -2244,7 +2244,7 @@
         <v>91</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>96</v>
@@ -2267,7 +2267,7 @@
         <v>93</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>96</v>
@@ -2290,7 +2290,7 @@
         <v>29</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>98</v>
@@ -2313,7 +2313,7 @@
         <v>33</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>98</v>
@@ -2336,7 +2336,7 @@
         <v>35</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>98</v>
@@ -2359,7 +2359,7 @@
         <v>37</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>98</v>
@@ -2382,7 +2382,7 @@
         <v>39</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>98</v>
@@ -2405,7 +2405,7 @@
         <v>41</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>98</v>
@@ -2428,7 +2428,7 @@
         <v>43</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>98</v>
@@ -2451,7 +2451,7 @@
         <v>45</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>98</v>
@@ -2474,7 +2474,7 @@
         <v>47</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>98</v>
@@ -2497,7 +2497,7 @@
         <v>49</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>98</v>
@@ -2520,7 +2520,7 @@
         <v>51</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>98</v>
@@ -2543,7 +2543,7 @@
         <v>53</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>98</v>
@@ -2566,7 +2566,7 @@
         <v>55</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>98</v>
@@ -2589,7 +2589,7 @@
         <v>57</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>98</v>
@@ -2612,7 +2612,7 @@
         <v>59</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>98</v>
@@ -2635,7 +2635,7 @@
         <v>61</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>98</v>
@@ -2658,7 +2658,7 @@
         <v>63</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>98</v>
@@ -2681,7 +2681,7 @@
         <v>65</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>98</v>
@@ -2704,7 +2704,7 @@
         <v>67</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>98</v>
@@ -2727,7 +2727,7 @@
         <v>69</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>98</v>
@@ -2750,7 +2750,7 @@
         <v>71</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>98</v>
@@ -2773,7 +2773,7 @@
         <v>73</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>98</v>
@@ -2796,7 +2796,7 @@
         <v>75</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>98</v>
@@ -2819,7 +2819,7 @@
         <v>77</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>98</v>
@@ -2842,7 +2842,7 @@
         <v>79</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>98</v>
@@ -2865,7 +2865,7 @@
         <v>81</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>98</v>
@@ -2888,7 +2888,7 @@
         <v>83</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>98</v>
@@ -2911,7 +2911,7 @@
         <v>85</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>98</v>
@@ -2934,7 +2934,7 @@
         <v>87</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>98</v>
@@ -2957,7 +2957,7 @@
         <v>89</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>98</v>
@@ -2980,7 +2980,7 @@
         <v>91</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>98</v>
@@ -3003,7 +3003,7 @@
         <v>93</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>98</v>
@@ -3026,7 +3026,7 @@
         <v>99</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>98</v>
@@ -3049,7 +3049,7 @@
         <v>102</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>103</v>
@@ -3072,7 +3072,7 @@
         <v>105</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>103</v>
@@ -3095,7 +3095,7 @@
         <v>107</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>103</v>
@@ -3118,7 +3118,7 @@
         <v>109</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>103</v>
@@ -3141,7 +3141,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>103</v>
@@ -3164,7 +3164,7 @@
         <v>113</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>103</v>
@@ -3187,7 +3187,7 @@
         <v>114</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>103</v>
@@ -3210,7 +3210,7 @@
         <v>116</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>103</v>
@@ -3233,7 +3233,7 @@
         <v>117</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>103</v>
@@ -3256,7 +3256,7 @@
         <v>119</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>103</v>
@@ -3279,7 +3279,7 @@
         <v>121</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>103</v>
@@ -3302,7 +3302,7 @@
         <v>123</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>103</v>
@@ -3325,7 +3325,7 @@
         <v>126</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>127</v>
@@ -3348,7 +3348,7 @@
         <v>129</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>127</v>
@@ -3371,7 +3371,7 @@
         <v>131</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>127</v>
@@ -3394,7 +3394,7 @@
         <v>57</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>127</v>
@@ -3417,7 +3417,7 @@
         <v>134</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>127</v>
@@ -3440,7 +3440,7 @@
         <v>136</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>127</v>
@@ -3463,7 +3463,7 @@
         <v>138</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>127</v>
@@ -3486,7 +3486,7 @@
         <v>134</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>141</v>
@@ -3509,7 +3509,7 @@
         <v>138</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>141</v>
@@ -3532,7 +3532,7 @@
         <v>126</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>141</v>
@@ -3555,7 +3555,7 @@
         <v>142</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>141</v>
@@ -3578,7 +3578,7 @@
         <v>144</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>141</v>
@@ -3601,7 +3601,7 @@
         <v>146</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>141</v>
@@ -3624,7 +3624,7 @@
         <v>148</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>141</v>
@@ -3647,7 +3647,7 @@
         <v>126</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>151</v>
@@ -3670,7 +3670,7 @@
         <v>129</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>151</v>
@@ -3693,7 +3693,7 @@
         <v>131</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>151</v>
@@ -3716,7 +3716,7 @@
         <v>142</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>151</v>
@@ -3739,7 +3739,7 @@
         <v>144</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>151</v>
@@ -3762,7 +3762,7 @@
         <v>146</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>151</v>
@@ -3785,7 +3785,7 @@
         <v>148</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>151</v>
@@ -3808,7 +3808,7 @@
         <v>152</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>151</v>
@@ -3831,7 +3831,7 @@
         <v>154</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>151</v>
@@ -3854,7 +3854,7 @@
         <v>157</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>158</v>
@@ -3877,7 +3877,7 @@
         <v>160</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>158</v>
@@ -3900,7 +3900,7 @@
         <v>162</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>158</v>
@@ -3923,7 +3923,7 @@
         <v>164</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>158</v>
